--- a/download/scandinavian-gym-leads-VERIFIED.xlsx
+++ b/download/scandinavian-gym-leads-VERIFIED.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -745,8 +745,16 @@
           <t>https://instagram.com/copenhagen_muay_thai</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Copenhagen</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Muay Thai</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1082,21 +1090,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Great to make it to Denmark.. Will be here a for a few weeks</t>
+          <t>Great Danes Fight Club | Kampsport i Odense</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>@havocmmabergen</t>
+          <t>@greatdanesfightclub</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://instagram.com/havocmmabergen</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+          <t>https://instagram.com/greatdanesfightclub</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Odense</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>BJJ</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1111,29 +1127,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hive BJJ</t>
+          <t>Great to make it to Denmark.. Will be here a for a few weeks</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>@hivebjj</t>
+          <t>@havocmmabergen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://instagram.com/hivebjj</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Copenhagen</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>BJJ</t>
-        </is>
-      </c>
+          <t>https://instagram.com/havocmmabergen</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1148,27 +1156,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Horsens Muay Thai | K-1 | MMA</t>
+          <t>Hive BJJ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>@horsensmuaythaik1</t>
+          <t>@hivebjj</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://instagram.com/horsensmuaythaik1</t>
+          <t>https://instagram.com/hivebjj</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Copenhagen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MMA</t>
+          <t>BJJ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1185,21 +1193,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISKA Denmark and @efldk present 5x ISKA titles in 10 </t>
+          <t>Horsens Muay Thai | K-1 | MMA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>@efldk</t>
+          <t>@horsensmuaythaik1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://instagram.com/efldk</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+          <t>https://instagram.com/horsensmuaythaik1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Horsens</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MMA</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1214,17 +1230,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Instagram for Creators: Frequently Asked Questions</t>
+          <t xml:space="preserve">ISKA Denmark and @efldk present 5x ISKA titles in 10 </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>@faq</t>
+          <t>@efldk</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://instagram.com/faq</t>
+          <t>https://instagram.com/efldk</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1243,17 +1259,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Iron Mike. Made in @prisoninkdk taking 3th place in Best realistic</t>
+          <t>Instagram for Creators: Frequently Asked Questions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>@prisoninkdk</t>
+          <t>@faq</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://instagram.com/prisoninkdk</t>
+          <t>https://instagram.com/faq</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1272,29 +1288,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JYLLINGE BOXING TEAM</t>
+          <t>Iron Mike. Made in @prisoninkdk taking 3th place in Best realistic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>@jyllinge_boxing_team_dk</t>
+          <t>@prisoninkdk</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://instagram.com/jyllinge_boxing_team_dk</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Roskilde</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>boxing</t>
-        </is>
-      </c>
+          <t>https://instagram.com/prisoninkdk</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1309,22 +1317,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jeet Kune Do København</t>
+          <t>JYLLINGE BOXING TEAM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>@jkdkbh</t>
+          <t>@jyllinge_boxing_team_dk</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://instagram.com/jkdkbh</t>
+          <t>https://instagram.com/jyllinge_boxing_team_dk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Frederiksberg</t>
+          <t>Roskilde</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1346,21 +1354,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Just watched the boxing legend @miketyson get beaten by a</t>
+          <t>Jeet Kune Do København</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>@mcguzto</t>
+          <t>@jkdkbh</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://instagram.com/mcguzto</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+          <t>https://instagram.com/jkdkbh</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Frederiksberg</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>boxing</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1375,25 +1391,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lucky Punch Copenhagen</t>
+          <t>Just watched the boxing legend @miketyson get beaten by a</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>@luckypunch.copenhagen</t>
+          <t>@mcguzto</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://instagram.com/luckypunch.copenhagen</t>
+          <t>https://instagram.com/mcguzto</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>boxing</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1408,27 +1420,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mielnikpiotr</t>
+          <t>Lucky Punch Copenhagen</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>@mielnikpiotr</t>
+          <t>@luckypunch.copenhagen</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://instagram.com/mielnikpiotr</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Aarhus</t>
-        </is>
-      </c>
+          <t>https://instagram.com/luckypunch.copenhagen</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BJJ</t>
+          <t>boxing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1445,27 +1453,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mike Foss</t>
+          <t>Mielnikpiotr</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>@_mike_foss</t>
+          <t>@mielnikpiotr</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://instagram.com/_mike_foss</t>
+          <t>https://instagram.com/mielnikpiotr</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Aarhus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MMA</t>
+          <t>BJJ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1482,21 +1490,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Muay Football 😅 Follow @muaythaimagic The Home Of</t>
+          <t>Mike Foss</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>@muaythaimagic</t>
+          <t>@_mike_foss</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://instagram.com/muaythaimagic</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+          <t>https://instagram.com/_mike_foss</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Horsens</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>MMA</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1511,29 +1527,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Muay Thai Gym</t>
+          <t>Muay Football 😅 Follow @muaythaimagic The Home Of</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>@blessed.performance</t>
+          <t>@muaythaimagic</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://instagram.com/blessed.performance</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Aarhus</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Muay Thai</t>
-        </is>
-      </c>
+          <t>https://instagram.com/muaythaimagic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1548,27 +1556,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nordic SFC</t>
+          <t>Muay Thai Gym</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>@nordic.sfc</t>
+          <t>@blessed.performance</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://instagram.com/nordic.sfc</t>
+          <t>https://instagram.com/blessed.performance</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kolding</t>
+          <t>Aarhus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BJJ</t>
+          <t>Muay Thai</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1585,27 +1593,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Odense Muay Thai</t>
+          <t>Nordic SFC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>@odensemuaythai</t>
+          <t>@nordic.sfc</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://instagram.com/odensemuaythai</t>
+          <t>https://instagram.com/nordic.sfc</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Odense</t>
+          <t>Kolding</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Muay Thai</t>
+          <t>BJJ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1622,27 +1630,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pan Boksning</t>
+          <t>Odense Bushido Klub</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>@pan.boxing</t>
+          <t>@teambushido_odense</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://instagram.com/pan.boxing</t>
+          <t>https://instagram.com/teambushido_odense</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Copenhagen</t>
+          <t>Odense</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>boxing</t>
+          <t>BJJ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1659,27 +1667,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RULES BOXING CLUB</t>
+          <t>Odense Muay Thai</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>@rulesboxingclub</t>
+          <t>@odensemuaythai</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://instagram.com/rulesboxingclub</t>
+          <t>https://instagram.com/odensemuaythai</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Copenhagen</t>
+          <t>Odense</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>boxing</t>
+          <t>Muay Thai</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1696,21 +1704,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Report convicted sex offenders on Instagram</t>
+          <t>Pan Boksning</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>@131932550339730</t>
+          <t>@pan.boxing</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://instagram.com/131932550339730</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>https://instagram.com/pan.boxing</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Copenhagen</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>boxing</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1725,23 +1741,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rolands GYM (RG)</t>
+          <t>RULES BOXING CLUB</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>@rolands_cph</t>
+          <t>@rulesboxingclub</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://instagram.com/rolands_cph</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>https://instagram.com/rulesboxingclub</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Copenhagen</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>martial arts</t>
+          <t>boxing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1758,29 +1778,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rumble Sports</t>
+          <t>Report convicted sex offenders on Instagram</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>@rumblesports</t>
+          <t>@131932550339730</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://instagram.com/rumblesports</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Frederiksberg</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>MMA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/131932550339730</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1795,21 +1807,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Solid 2 days of training wit dis Viking Hammah ⚒️💥🥊 @stompel.</t>
+          <t>Rolands GYM (RG)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>@stompel.art</t>
+          <t>@rolands_cph</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://instagram.com/stompel.art</t>
+          <t>https://instagram.com/rolands_cph</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>martial arts</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1824,23 +1840,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sporting Health Club | Beyond Fitness</t>
+          <t>Rumble Sports</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>@sportinghealthclub</t>
+          <t>@rumblesports</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://instagram.com/sportinghealthclub</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>https://instagram.com/rumblesports</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Frederiksberg</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>boxing</t>
+          <t>MMA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1857,17 +1877,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TITO DOUBLE P 👹</t>
+          <t>Solid 2 days of training wit dis Viking Hammah ⚒️💥🥊 @stompel.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>@titodoublep</t>
+          <t>@stompel.art</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://instagram.com/titodoublep</t>
+          <t>https://instagram.com/stompel.art</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1886,21 +1906,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">The baddest muaythai woman on planet earth </t>
+          <t>Sporting Health Club | Beyond Fitness</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>@_sarahmahfoud</t>
+          <t>@sportinghealthclub</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://instagram.com/_sarahmahfoud</t>
+          <t>https://instagram.com/sportinghealthclub</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>boxing</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1915,17 +1939,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>To be a champ, you got to eat like one 🍳👊🏽 #food #eggs</t>
+          <t>TITO DOUBLE P 👹</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>@gillelejebokseklub</t>
+          <t>@titodoublep</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://instagram.com/gillelejebokseklub</t>
+          <t>https://instagram.com/titodoublep</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1944,17 +1968,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TuffNuff | Get ready with Luca Later this week, nine Eastside boxers</t>
+          <t xml:space="preserve">The baddest muaythai woman on planet earth </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>@tuff_nuff_boxing_tournament</t>
+          <t>@_sarahmahfoud</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://instagram.com/tuff_nuff_boxing_tournament</t>
+          <t>https://instagram.com/_sarahmahfoud</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -1973,17 +1997,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Update your name, email and other personal information</t>
+          <t>To be a champ, you got to eat like one 🍳👊🏽 #food #eggs</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>@356648689595660</t>
+          <t>@gillelejebokseklub</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://instagram.com/356648689595660</t>
+          <t>https://instagram.com/gillelejebokseklub</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2002,17 +2026,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>WBC MuayThai on Instagram: "And New Danish Nak Muay Frederik</t>
+          <t>TuffNuff | Get ready with Luca Later this week, nine Eastside boxers</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>@unite_championship</t>
+          <t>@tuff_nuff_boxing_tournament</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://instagram.com/unite_championship</t>
+          <t>https://instagram.com/tuff_nuff_boxing_tournament</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2031,29 +2055,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>fight.team.kolding</t>
+          <t>Update your name, email and other personal information</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>@fight.team.kolding</t>
+          <t>@356648689595660</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://instagram.com/fight.team.kolding</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Kolding</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>BJJ</t>
-        </is>
-      </c>
+          <t>https://instagram.com/356648689595660</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2068,17 +2084,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>teenagers and barely adults with no idea of</t>
+          <t>WBC MuayThai on Instagram: "And New Danish Nak Muay Frederik</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>@__.i.nes.__</t>
+          <t>@unite_championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://instagram.com/__.i.nes.__</t>
+          <t>https://instagram.com/unite_championship</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2090,28 +2106,36 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Norway</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Apex MMA</t>
+          <t>fight.team.kolding</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>@mudogymcarlberner</t>
+          <t>@fight.team.kolding</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://instagram.com/mudogymcarlberner</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+          <t>https://instagram.com/fight.team.kolding</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Kolding</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>BJJ</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2119,28 +2143,36 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Norway</t>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>At our center @trondheim_kampsport you can train Jiu-Jitsu</t>
+          <t>killbox jiu-jitsu</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>@trondheim_kampsport</t>
+          <t>@killboxjiujitsu</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://instagram.com/trondheim_kampsport</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+          <t>https://instagram.com/killboxjiujitsu</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Horsens</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BJJ</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2148,28 +2180,36 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Norway</t>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Became a smal part of the team @frontlinedrammen. New</t>
+          <t>odense.submission.fighting</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>@frontlinedrammen.</t>
+          <t>@odense.submission.fighting</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://instagram.com/frontlinedrammen.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+          <t>https://instagram.com/odense.submission.fighting</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Odense</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>BJJ</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2177,36 +2217,28 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Norway</t>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Benjamin Hauser</t>
+          <t>teenagers and barely adults with no idea of</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>@panzerhauser</t>
+          <t>@__.i.nes.__</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://instagram.com/panzerhauser</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Oslo</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>MMA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/__.i.nes.__</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2221,17 +2253,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bodø MMA</t>
+          <t>Apex MMA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>@bodommaofficial</t>
+          <t>@mudogymcarlberner</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://instagram.com/bodommaofficial</t>
+          <t>https://instagram.com/mudogymcarlberner</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2250,25 +2282,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CrossFight Academy Norway</t>
+          <t>At our center @trondheim_kampsport you can train Jiu-Jitsu</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>@crossfightacademynorway</t>
+          <t>@trondheim_kampsport</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://instagram.com/crossfightacademynorway</t>
+          <t>https://instagram.com/trondheim_kampsport</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>BJJ</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2283,17 +2311,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Erkin Tasdelen</t>
+          <t>Became a smal part of the team @frontlinedrammen. New</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>@erkin_tasdelen</t>
+          <t>@frontlinedrammen.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://instagram.com/erkin_tasdelen</t>
+          <t>https://instagram.com/frontlinedrammen.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2312,21 +2340,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FitnessFirst Bergen</t>
+          <t>Benjamin Hauser</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>@fitnessfirstbergen</t>
+          <t>@panzerhauser</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://instagram.com/fitnessfirstbergen</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+          <t>https://instagram.com/panzerhauser</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>MMA</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2341,17 +2377,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Frontline Academy Bergen</t>
+          <t>Bodø MMA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>@frontlinebergen</t>
+          <t>@bodommaofficial</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://instagram.com/frontlinebergen</t>
+          <t>https://instagram.com/bodommaofficial</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2370,24 +2406,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ippon Judo &amp; BJJ</t>
+          <t>CrossFight Academy Norway</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>@ippon_judo_bjj</t>
+          <t>@crossfightacademynorway</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://instagram.com/ippon_judo_bjj</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Oslo</t>
-        </is>
-      </c>
+          <t>https://instagram.com/crossfightacademynorway</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>BJJ</t>
@@ -2407,29 +2439,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jiu-Jitsu Collective</t>
+          <t>Erkin Tasdelen</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>@jiujitsucollective.oslo</t>
+          <t>@erkin_tasdelen</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://instagram.com/jiujitsucollective.oslo</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Oslo</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>BJJ</t>
-        </is>
-      </c>
+          <t>https://instagram.com/erkin_tasdelen</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2444,29 +2468,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KORU MARTIAL ARTS</t>
+          <t>FitnessFirst Bergen</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>@koru_martialarts</t>
+          <t>@fitnessfirstbergen</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://instagram.com/koru_martialarts</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Oslo</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>MMA</t>
-        </is>
-      </c>
+          <t>https://instagram.com/fitnessfirstbergen</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2481,25 +2497,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OXYGYM</t>
+          <t>Frontline Academy Bergen</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>@oxygymnorway</t>
+          <t>@frontlinebergen</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://instagram.com/oxygymnorway</t>
+          <t>https://instagram.com/frontlinebergen</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>BJJ</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2514,17 +2526,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Oslo MMA Academy</t>
+          <t>Ippon Judo &amp; BJJ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>@oslo_mma_academy</t>
+          <t>@ippon_judo_bjj</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://instagram.com/oslo_mma_academy</t>
+          <t>https://instagram.com/ippon_judo_bjj</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2534,7 +2546,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MMA</t>
+          <t>BJJ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2551,21 +2563,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Reel by Roger Eriksen</t>
+          <t>Jiu-Jitsu Collective</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>@yahoo.com</t>
+          <t>@jiujitsucollective.oslo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://instagram.com/yahoo.com</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+          <t>https://instagram.com/jiujitsucollective.oslo</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>BJJ</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2580,21 +2600,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Roger Eriksen</t>
+          <t>KORU MARTIAL ARTS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>@coachroger70</t>
+          <t>@koru_martialarts</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://instagram.com/coachroger70</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+          <t>https://instagram.com/koru_martialarts</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>MMA</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2609,21 +2637,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sotra Muay Thai Gym</t>
+          <t>OXYGYM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>@sotramuaythai</t>
+          <t>@oxygymnorway</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://instagram.com/sotramuaythai</t>
+          <t>https://instagram.com/oxygymnorway</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>BJJ</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2638,23 +2670,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tarik Hopstock</t>
+          <t>Oslo MMA Academy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>@tarik_bjj</t>
+          <t>@oslo_mma_academy</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://instagram.com/tarik_bjj</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+          <t>https://instagram.com/oslo_mma_academy</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BJJ</t>
+          <t>MMA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2671,17 +2707,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Team Carvalho Drammen BJJ</t>
+          <t>Reel by Roger Eriksen</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>@teamcarvalho_drammen</t>
+          <t>@yahoo.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://instagram.com/teamcarvalho_drammen</t>
+          <t>https://instagram.com/yahoo.com</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -2700,17 +2736,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tommi McCormick</t>
+          <t>Roger Eriksen</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>@tommi_mccormick</t>
+          <t>@coachroger70</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://instagram.com/tommi_mccormick</t>
+          <t>https://instagram.com/coachroger70</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -2729,17 +2765,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Welcome to my beautiful gym, if you are ever in Norway come check</t>
+          <t>Sotra Muay Thai Gym</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>@heatfitnessclub</t>
+          <t>@sotramuaythai</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://instagram.com/heatfitnessclub</t>
+          <t>https://instagram.com/sotramuaythai</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -2751,28 +2787,32 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>Sweden</t>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>#mma #mmaamateur #fight #training #mmabasic #helsingborg #</t>
+          <t>Tarik Hopstock</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>@alancarlosjj</t>
+          <t>@tarik_bjj</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://instagram.com/alancarlosjj</t>
+          <t>https://instagram.com/tarik_bjj</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>BJJ</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2780,24 +2820,24 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>Sweden</t>
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>#rakennusliiketeräksinenoy @karkisahko_oy @</t>
+          <t>Team Carvalho Drammen BJJ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>@jacyzhotel.</t>
+          <t>@teamcarvalho_drammen</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://instagram.com/jacyzhotel.</t>
+          <t>https://instagram.com/teamcarvalho_drammen</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -2809,24 +2849,24 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>Sweden</t>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>019 Boxing Gym</t>
+          <t>Tommi McCormick</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>@019boxinggym</t>
+          <t>@tommi_mccormick</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://instagram.com/019boxinggym</t>
+          <t>https://instagram.com/tommi_mccormick</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -2838,24 +2878,24 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>Sweden</t>
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Advertising @latitude_65 Pre training drink always . #muaythai</t>
+          <t>Welcome to my beautiful gym, if you are ever in Norway come check</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>@latitude_65</t>
+          <t>@heatfitnessclub</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://instagram.com/latitude_65</t>
+          <t>https://instagram.com/heatfitnessclub</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -2874,17 +2914,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Allstars Training Center</t>
+          <t>#mma #mmaamateur #fight #training #mmabasic #helsingborg #</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>@allstarsgymsweden</t>
+          <t>@alancarlosjj</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://instagram.com/allstarsgymsweden</t>
+          <t>https://instagram.com/alancarlosjj</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -2903,17 +2943,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ammar</t>
+          <t>#rakennusliiketeräksinenoy @karkisahko_oy @</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>@ammar_nmnm</t>
+          <t>@jacyzhotel.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://instagram.com/ammar_nmnm</t>
+          <t>https://instagram.com/jacyzhotel.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -2932,17 +2972,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Andreas Michael</t>
+          <t>019 Boxing Gym</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>@andreasthegeneral</t>
+          <t>@019boxinggym</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://instagram.com/andreasthegeneral</t>
+          <t>https://instagram.com/019boxinggym</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2961,17 +3001,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Arturs Ozolins</t>
+          <t>Advertising @latitude_65 Pre training drink always . #muaythai</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>@arturs_ozolins</t>
+          <t>@latitude_65</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://instagram.com/arturs_ozolins</t>
+          <t>https://instagram.com/latitude_65</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -2990,17 +3030,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Brickhouse Boxing Club</t>
+          <t>Allstars Training Center</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>@brickhouseboxingclub</t>
+          <t>@allstarsgymsweden</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://instagram.com/brickhouseboxingclub</t>
+          <t>https://instagram.com/allstarsgymsweden</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3019,17 +3059,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CONFIRMED the home town favorite @georgeyousseff</t>
+          <t>Ammar</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>@georgeyousseff</t>
+          <t>@ammar_nmnm</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://instagram.com/georgeyousseff</t>
+          <t>https://instagram.com/ammar_nmnm</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3048,17 +3088,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Chasing a Dream Through Boxing</t>
+          <t>Andreas Michael</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>@flow_boxing</t>
+          <t>@andreasthegeneral</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://instagram.com/flow_boxing</t>
+          <t>https://instagram.com/andreasthegeneral</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3077,17 +3117,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fight Center Linköping</t>
+          <t>Arturs Ozolins</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>@fight_center</t>
+          <t>@arturs_ozolins</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://instagram.com/fight_center</t>
+          <t>https://instagram.com/arturs_ozolins</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3106,17 +3146,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Fighting is Golden</t>
+          <t>Brickhouse Boxing Club</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>@goldenfightclub.se</t>
+          <t>@brickhouseboxingclub</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://instagram.com/goldenfightclub.se</t>
+          <t>https://instagram.com/brickhouseboxingclub</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3135,17 +3175,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Golden Leaf 🍁Muaythai, Malmo, Sweden #timoreseassassin</t>
+          <t>CONFIRMED the home town favorite @georgeyousseff</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>@muaythaivictoria.</t>
+          <t>@georgeyousseff</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://instagram.com/muaythaivictoria.</t>
+          <t>https://instagram.com/georgeyousseff</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3164,17 +3204,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>I R F A</t>
+          <t>Chasing a Dream Through Boxing</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>@irfa_official</t>
+          <t>@flow_boxing</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://instagram.com/irfa_official</t>
+          <t>https://instagram.com/flow_boxing</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3193,17 +3233,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>It's fight week, and here is the official fight card for FCR27👊</t>
+          <t>Fight Center Linköping</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>@ufcfightpass</t>
+          <t>@fight_center</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://instagram.com/ufcfightpass</t>
+          <t>https://instagram.com/fight_center</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3222,17 +3262,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JOHANNA PERSSON MUAY THAI 🇸🇪</t>
+          <t>Fighting is Golden</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>@johannakpersson</t>
+          <t>@goldenfightclub.se</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://instagram.com/johannakpersson</t>
+          <t>https://instagram.com/goldenfightclub.se</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -3251,17 +3291,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KNUCKLE SPORTS PROMOTION</t>
+          <t>Golden Leaf 🍁Muaythai, Malmo, Sweden #timoreseassassin</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>@ksp_promotions</t>
+          <t>@muaythaivictoria.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://instagram.com/ksp_promotions</t>
+          <t>https://instagram.com/muaythaivictoria.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3280,17 +3320,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>King of the Ring</t>
+          <t>I R F A</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>@kingoftheringbox</t>
+          <t>@irfa_official</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://instagram.com/kingoftheringbox</t>
+          <t>https://instagram.com/irfa_official</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -3309,17 +3349,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Larry Lindwall</t>
+          <t>It's fight week, and here is the official fight card for FCR27👊</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>@larry_lindwall</t>
+          <t>@ufcfightpass</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://instagram.com/larry_lindwall</t>
+          <t>https://instagram.com/ufcfightpass</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3338,17 +3378,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Malin Hermansson</t>
+          <t>JOHANNA PERSSON MUAY THAI 🇸🇪</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>@mghermansson</t>
+          <t>@johannakpersson</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://instagram.com/mghermansson</t>
+          <t>https://instagram.com/johannakpersson</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3367,17 +3407,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Malmö Boxing Academy</t>
+          <t>KNUCKLE SPORTS PROMOTION</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>@malmoboxingacademy</t>
+          <t>@ksp_promotions</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://instagram.com/malmoboxingacademy</t>
+          <t>https://instagram.com/ksp_promotions</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -3396,17 +3436,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mark Stewart</t>
+          <t>King of the Ring</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>@markfightingfit</t>
+          <t>@kingoftheringbox</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://instagram.com/markfightingfit</t>
+          <t>https://instagram.com/kingoftheringbox</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -3425,17 +3465,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Onwards and upwards, together 👋🏻 @holmgrensfoto #</t>
+          <t>Larry Lindwall</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>@jonkopingmarathon</t>
+          <t>@larry_lindwall</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://instagram.com/jonkopingmarathon</t>
+          <t>https://instagram.com/larry_lindwall</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -3454,17 +3494,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RUMBLE ON THE RIVER</t>
+          <t>Malin Hermansson</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>@rumbleontheriverofficial</t>
+          <t>@mghermansson</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://instagram.com/rumbleontheriverofficial</t>
+          <t>https://instagram.com/mghermansson</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -3483,17 +3523,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Stark jiu jitsu</t>
+          <t>Malmö Boxing Academy</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>@bestpracticebjj</t>
+          <t>@malmoboxingacademy</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://instagram.com/bestpracticebjj</t>
+          <t>https://instagram.com/malmoboxingacademy</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -3512,17 +3552,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Stockholm Muay Thai #TEAMSMT</t>
+          <t>Mark Stewart</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>@stockholm_muaythai</t>
+          <t>@markfightingfit</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://instagram.com/stockholm_muaythai</t>
+          <t>https://instagram.com/markfightingfit</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3541,17 +3581,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tiger Eye Boxing</t>
+          <t>Onwards and upwards, together 👋🏻 @holmgrensfoto #</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>@tigereyeboxing</t>
+          <t>@jonkopingmarathon</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://instagram.com/tigereyeboxing</t>
+          <t>https://instagram.com/jonkopingmarathon</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -3570,17 +3610,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>[collaboration] Can't wait to fight soon! 🔥 All gear</t>
+          <t>RUMBLE ON THE RIVER</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>@rdx_sports</t>
+          <t>@rumbleontheriverofficial</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://instagram.com/rdx_sports</t>
+          <t>https://instagram.com/rumbleontheriverofficial</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -3599,17 +3639,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ericssonsamuel</t>
+          <t>Stark jiu jitsu</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>@ericssonsamuel</t>
+          <t>@bestpracticebjj</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://instagram.com/ericssonsamuel</t>
+          <t>https://instagram.com/bestpracticebjj</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -3628,17 +3668,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>newswedenboxingfederation</t>
+          <t>Stockholm Muay Thai #TEAMSMT</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>@newswedenboxingfederation</t>
+          <t>@stockholm_muaythai</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://instagram.com/newswedenboxingfederation</t>
+          <t>https://instagram.com/stockholm_muaythai</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -3657,17 +3697,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>sannydahlbeck</t>
+          <t>Tiger Eye Boxing</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>@sannydahlbeck</t>
+          <t>@tigereyeboxing</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://instagram.com/sannydahlbeck</t>
+          <t>https://instagram.com/tigereyeboxing</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -3686,17 +3726,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>supreme.gym</t>
+          <t>[collaboration] Can't wait to fight soon! 🔥 All gear</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>@supreme.gym</t>
+          <t>@rdx_sports</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://instagram.com/supreme.gym</t>
+          <t>https://instagram.com/rdx_sports</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -3715,17 +3755,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Örebro Boxningsklubb</t>
+          <t>ericssonsamuel</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>@orebrobk</t>
+          <t>@ericssonsamuel</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://instagram.com/orebrobk</t>
+          <t>https://instagram.com/ericssonsamuel</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -3744,17 +3784,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Örebro Fight Gym</t>
+          <t>newswedenboxingfederation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>@orebro_fightgym</t>
+          <t>@newswedenboxingfederation</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://instagram.com/orebro_fightgym</t>
+          <t>https://instagram.com/newswedenboxingfederation</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -3773,17 +3813,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Öresund Muay Thai Camp</t>
+          <t>sannydahlbeck</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>@oresund_muay_thai_camp</t>
+          <t>@sannydahlbeck</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://instagram.com/oresund_muay_thai_camp</t>
+          <t>https://instagram.com/sannydahlbeck</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -3802,17 +3842,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>⚠️FIGHT ANNOUNCEMENT⚠️ It's time for Sweden vs</t>
+          <t>supreme.gym</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>@akiracorassani.</t>
+          <t>@supreme.gym</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://instagram.com/akiracorassani.</t>
+          <t>https://instagram.com/supreme.gym</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
@@ -3831,17 +3871,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>💥Fight week💥 🥊6 rounds lightweight Paolo Magui, team</t>
+          <t>Örebro Boxningsklubb</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>@bkringenboxning.</t>
+          <t>@orebrobk</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://instagram.com/bkringenboxning.</t>
+          <t>https://instagram.com/orebrobk</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -3860,22 +3900,138 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>📆 Saturday, September 19 @oscarahlin Oscar Ahlin 🆚</t>
+          <t>Örebro Fight Gym</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>@oscarahlin</t>
+          <t>@orebro_fightgym</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://instagram.com/oscarahlin</t>
+          <t>https://instagram.com/orebro_fightgym</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Öresund Muay Thai Camp</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>@oresund_muay_thai_camp</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://instagram.com/oresund_muay_thai_camp</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>⚠️FIGHT ANNOUNCEMENT⚠️ It's time for Sweden vs</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>@akiracorassani.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://instagram.com/akiracorassani.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>💥Fight week💥 🥊6 rounds lightweight Paolo Magui, team</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>@bkringenboxning.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://instagram.com/bkringenboxning.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>📆 Saturday, September 19 @oscarahlin Oscar Ahlin 🆚</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>@oscarahlin</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://instagram.com/oscarahlin</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3932,7 +4088,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -3962,7 +4118,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
